--- a/RPROCL.xlsx
+++ b/RPROCL.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20070539</t>
-  </si>
-  <si>
-    <t>AICE CHOCO CRPSY 60G</t>
+    <t>20134926</t>
+  </si>
+  <si>
+    <t>WALL ICE CRM OREO 80</t>
   </si>
   <si>
     <t>RPROCL</t>
@@ -28,70 +28,46 @@
     <t>4</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20128377</t>
-  </si>
-  <si>
-    <t>CMPN ICE CSHW NUT90</t>
-  </si>
-  <si>
-    <t>145</t>
+    <t>184</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20125168</t>
-  </si>
-  <si>
-    <t>WALL FST POP VN&amp;CR64</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>20138191</t>
-  </si>
-  <si>
-    <t>WALL FST POP STR</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>20140730</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO BROWNIE</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>20138568</t>
-  </si>
-  <si>
-    <t>MOOOCHII RED BEAN40G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>20138569</t>
-  </si>
-  <si>
-    <t>MOOOCHII CHOCO 40G</t>
-  </si>
-  <si>
-    <t>184</t>
+    <t>20139460</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO HZL 108</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>20139189</t>
+  </si>
+  <si>
+    <t>WALLS SOLERO P&amp;L 65</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>20140720</t>
+  </si>
+  <si>
+    <t>CMPN OCHEESECAKE 90</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>20141544</t>
+  </si>
+  <si>
+    <t>WALLS CLP PEACHMG100</t>
+  </si>
+  <si>
+    <t>260</t>
   </si>
 </sst>
 </file>
@@ -484,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -552,15 +528,15 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -569,18 +545,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -589,18 +565,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -609,50 +585,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/RPROCL.xlsx
+++ b/RPROCL.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>20134926</t>
-  </si>
-  <si>
-    <t>WALL ICE CRM OREO 80</t>
+    <t>20126683</t>
+  </si>
+  <si>
+    <t>AICE HSTERIA VNLA 70</t>
   </si>
   <si>
     <t>RPROCL</t>
@@ -28,46 +28,40 @@
     <t>4</t>
   </si>
   <si>
-    <t>184</t>
+    <t>123</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137107</t>
+  </si>
+  <si>
+    <t>CMPNA HEART CRNCH 88</t>
+  </si>
+  <si>
+    <t>197</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139460</t>
-  </si>
-  <si>
-    <t>CORNETTO CHO HZL 108</t>
-  </si>
-  <si>
-    <t>234</t>
-  </si>
-  <si>
-    <t>20139189</t>
-  </si>
-  <si>
-    <t>WALLS SOLERO P&amp;L 65</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>20140720</t>
-  </si>
-  <si>
-    <t>CMPN OCHEESECAKE 90</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>20141544</t>
-  </si>
-  <si>
-    <t>WALLS CLP PEACHMG100</t>
-  </si>
-  <si>
-    <t>260</t>
+    <t>20136574</t>
+  </si>
+  <si>
+    <t>AICE HSTRIA MTCHA 70</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>20140183</t>
+  </si>
+  <si>
+    <t>WALLS X PC PSL 90ML</t>
+  </si>
+  <si>
+    <t>242</t>
   </si>
 </sst>
 </file>
@@ -460,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -528,15 +522,15 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -545,18 +539,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -565,30 +559,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/RPROCL.xlsx
+++ b/RPROCL.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20126683</t>
-  </si>
-  <si>
-    <t>AICE HSTERIA VNLA 70</t>
+    <t>20115639</t>
+  </si>
+  <si>
+    <t>WALLS OREO VNL90</t>
   </si>
   <si>
     <t>RPROCL</t>
@@ -28,33 +28,24 @@
     <t>4</t>
   </si>
   <si>
-    <t>123</t>
+    <t>71</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20137107</t>
-  </si>
-  <si>
-    <t>CMPNA HEART CRNCH 88</t>
-  </si>
-  <si>
-    <t>197</t>
+    <t>20135228</t>
+  </si>
+  <si>
+    <t>AICE CRISPY BALLS 65</t>
+  </si>
+  <si>
+    <t>187</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20136574</t>
-  </si>
-  <si>
-    <t>AICE HSTRIA MTCHA 70</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
     <t>20140183</t>
   </si>
   <si>
@@ -62,6 +53,33 @@
   </si>
   <si>
     <t>242</t>
+  </si>
+  <si>
+    <t>20139397</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL CNC 65</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>20138342</t>
+  </si>
+  <si>
+    <t>KALULI CHO MASTER 60</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>20142998</t>
+  </si>
+  <si>
+    <t>AICE CRS BALL MSCT65</t>
+  </si>
+  <si>
+    <t>261</t>
   </si>
 </sst>
 </file>
@@ -454,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -565,6 +583,46 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/RPROCL.xlsx
+++ b/RPROCL.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20115639</t>
-  </si>
-  <si>
-    <t>WALLS OREO VNL90</t>
+    <t>20140730</t>
+  </si>
+  <si>
+    <t>CORNETTO CHO BROWNIE</t>
   </si>
   <si>
     <t>RPROCL</t>
@@ -28,42 +28,12 @@
     <t>4</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20135228</t>
-  </si>
-  <si>
-    <t>AICE CRISPY BALLS 65</t>
-  </si>
-  <si>
-    <t>187</t>
+    <t>247</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20140183</t>
-  </si>
-  <si>
-    <t>WALLS X PC PSL 90ML</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>20139397</t>
-  </si>
-  <si>
-    <t>AICE CRS BALL CNC 65</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
     <t>20138342</t>
   </si>
   <si>
@@ -71,15 +41,6 @@
   </si>
   <si>
     <t>249</t>
-  </si>
-  <si>
-    <t>20142998</t>
-  </si>
-  <si>
-    <t>AICE CRS BALL MSCT65</t>
-  </si>
-  <si>
-    <t>261</t>
   </si>
 </sst>
 </file>
@@ -472,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -540,87 +501,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/RPROCL.xlsx
+++ b/RPROCL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
@@ -32,15 +32,6 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138342</t>
-  </si>
-  <si>
-    <t>KALULI CHO MASTER 60</t>
-  </si>
-  <si>
-    <t>249</t>
   </si>
 </sst>
 </file>
@@ -433,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -484,26 +475,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
